--- a/各工种场地课表_最新版03082.xlsx
+++ b/各工种场地课表_最新版03082.xlsx
@@ -905,7 +905,7 @@
 交通运输25(2) A机3-4
 ------------------
 【下午】
-能源动力类25(6) B机5-7（辛）</t>
+能源动力类25(6) B机5-7</t>
         </is>
       </c>
     </row>
@@ -1012,8 +1012,8 @@
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>【上午】
-能源化学工程24(1) B机1-2（郭）
-能源化学工程24(1) A机3-4（郭）
+能源化学工程24(1) B机1-2
+能源化学工程24(1) A机3-4
 ------------------
 【下午】
 微电子科学与工程24(2) B机5-6'
@@ -1023,8 +1023,8 @@
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>【上午】
-光电信息科学与工程24(1) B机1-2（郭）
-光电信息科学与工程24(1) A机3-4（郭）
+光电信息科学与工程24(1) B机1-2
+光电信息科学与工程24(1) A机3-4
 ------------------
 【下午】</t>
         </is>
@@ -1058,8 +1058,8 @@
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-化学工程与工艺(创新班)24(1) B机1-2（郭）
-化学工程与工艺(创新班)24(1) A机3-4（郭）
+化学工程与工艺(创新班)24(1) B机1-2
+化学工程与工艺(创新班)24(1) A机3-4
 ------------------
 【下午】</t>
         </is>
@@ -1067,7 +1067,7 @@
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-华师2 B机1-4（郭）
+华师2 B机1-4
 ------------------
 【下午】</t>
         </is>
@@ -1075,8 +1075,8 @@
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-电子科学与技术24(4) B机1-2（郭）
-电子科学与技术24(4) A机3-4（郭）
+电子科学与技术24(4) B机1-2
+电子科学与技术24(4) A机3-4
 ------------------
 【下午】
 电子科学与技术24(3) B机5-6'
@@ -1093,8 +1093,8 @@
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>【上午】
-环境生态工程25(1) B机1-2（郭）
-环境生态工程25(1) A机3-4（郭）
+环境生态工程25(1) B机1-2
+环境生态工程25(1) A机3-4
 ------------------
 【下午】
 能源动力类25(4) B机5-7</t>
@@ -1112,8 +1112,8 @@
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>【上午】
-工业工程24(2) B机1-2（李）
-工业工程24(2) A机3-4（李）
+工业工程24(2) B机1-2
+工业工程24(2) A机3-4
 ------------------
 【下午】
 微电子科学与工程24(1) B机5-6'
@@ -1131,8 +1131,8 @@
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>【上午】
-电子科学与技术24(2) B机1-2（辛）
-电子科学与技术24(2) A机3-4（辛）
+电子科学与技术24(2) B机1-2
+电子科学与技术24(2) A机3-4
 ------------------
 【下午】
 电子科学与技术(创新班)24(1) A机5-6'
@@ -1697,7 +1697,7 @@
 交通运输25(2) B柔3-4
 ------------------
 【下午】
-能源动力类25(5) B柔5-7（黄）</t>
+能源动力类25(5) B柔5-7</t>
         </is>
       </c>
     </row>
@@ -1782,10 +1782,10 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-电子科学与技术(创新班)24(1) B柔1-7
-------------------
-【下午】
-电子科学与技术(创新班)24(1) B柔1-7</t>
+电子科学与技术(创新班)24(1) B柔1-4
+------------------
+【下午】
+电子科学与技术(创新班)24(1) A柔5-7</t>
         </is>
       </c>
     </row>
@@ -1826,10 +1826,10 @@
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>【上午】
-电子科学与技术(创新班)24(1) A柔1-7
-------------------
-【下午】
-电子科学与技术(创新班)24(1) A柔1-7</t>
+电子科学与技术(创新班)24(1) B柔1-4
+------------------
+【下午】
+电子科学与技术(创新班)24(1) A柔5-7</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
 ------------------
 【下午】
 金融工程24(2) B激②5-6'
-金融工程24(2) A激②6'-7</t>
+金融工程24(2) A激②6'-8</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -2856,8 +2856,8 @@
           <t>【上午】
 ------------------
 【下午】
-电子科学与技术24(2) B激②5-6'（柏）
-电子科学与技术24(2) A激②6'-7（柏）</t>
+电子科学与技术24(2) B激②5-6'
+电子科学与技术24(2) A激②6'-7</t>
         </is>
       </c>
     </row>
@@ -2898,15 +2898,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>【上午】
-------------------
-【下午】
-应用化学24(4) A激②5-6'
-应用化学24(4) B激②6'-7</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
@@ -3098,7 +3090,15 @@
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>【上午】
+------------------
+【下午】
+应用化学24(4) A激②5-6'
+应用化学24(4) B激②6'-7</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
@@ -3282,7 +3282,7 @@
 ------------------
 【下午】
 金融工程24(1) B热5-6'
-金融工程24(1) A热6'-7</t>
+金融工程24(1) A热6'-8</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
@@ -3359,12 +3359,10 @@
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-应用化学24(2) B热1-2（胡）
-应用化学24(2) A热3-4（胡）
-------------------
-【下午】
-环境生态工程(创新班)25(1) B热5-6'（胡）
-环境生态工程(创新班)25(1) A热6'-7（胡）</t>
+------------------
+【下午】
+环境生态工程(创新班)25(1) B热5-6'
+环境生态工程(创新班)25(1) A热6'-7</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -3374,8 +3372,8 @@
           <t>【上午】
 ------------------
 【下午】
-能源动力类25(5) B热5-6'（林）
-能源动力类25(5) A热6'-7（林）</t>
+能源动力类25(5) B热5-6'
+能源动力类25(5) A热6'-7</t>
         </is>
       </c>
     </row>
@@ -3394,14 +3392,22 @@
 能源动力类25(1) A热6'-7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>【上午】
+应用化学24(2) B热1-2(胡)
+应用化学24(2) A热3-4(胡)
+------------------
+【下午】</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>【上午】
 ------------------
 【下午】
-微电子科学与工程24(4) B热5-6'（胡）
-微电子科学与工程24(4) A热6'-7（胡）</t>
+微电子科学与工程24(4) B热5-6'
+微电子科学与工程24(4) A热6'-7</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -3425,8 +3431,8 @@
       <c r="C9" s="3" t="inlineStr">
         <is>
           <t>【上午】
-应用化学24(1) B热1-2（胡）
-应用化学24(1) A热3-4（胡）
+应用化学24(1) B热1-2
+应用化学24(1) A热3-4
 ------------------
 【下午】</t>
         </is>
@@ -3436,8 +3442,8 @@
           <t>【上午】
 ------------------
 【下午】
-微电子科学与工程24(2) B热5-6'（林）
-微电子科学与工程24(2) A热6'-7（林）</t>
+微电子科学与工程24(2) B热5-6'
+微电子科学与工程24(2) A热6'-7</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3445,8 +3451,8 @@
           <t>【上午】
 ------------------
 【下午】
-能源动力类25(3) B热5-6'（胡）
-能源动力类25(3) A热6'-7（胡）</t>
+能源动力类25(3) B热5-6'
+能源动力类25(3) A热6'-7</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -5119,15 +5125,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>【上午】
-环境工程25(1) B装1-2
-环境工程25(1) A装3-4
-------------------
-【下午】</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
@@ -5150,10 +5148,10 @@
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-------------------
-【下午】
-应用化学24(4) B装5-6'
-应用化学24(4) A装6'-7</t>
+环境工程25(1) B装1-2
+环境工程25(1) A装3-4
+------------------
+【下午】</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
@@ -5409,7 +5407,15 @@
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>【上午】
+------------------
+【下午】
+应用化学24(4) B装5-6'
+应用化学24(4) A装6'-7</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>【上午】
@@ -6481,7 +6487,7 @@
 ------------------
 【下午】
 金融工程24(2) A超5-6'
-金融工程24(2) B超6'-7</t>
+金融工程24(2) B超6'-8</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -6498,8 +6504,8 @@
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>【上午】
-数字经济23(1) A超1-2（郭）
-数字经济23(1) B超3-4（郭）
+数字经济23(1) A超1-2
+数字经济23(1) B超3-4
 ------------------
 【下午】</t>
         </is>
@@ -6948,7 +6954,8 @@
           <t>【上午】
 应用化学24(1) 车1-4
 ------------------
-【下午】</t>
+【下午】
+环境科学25(1) 车5-7</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -6994,7 +7001,6 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>【上午】
-环境工程25(2) 车1-4
 ------------------
 【下午】
 应用化学24(4) 车5-7</t>
@@ -7047,8 +7053,7 @@
 材料类(创新班)24(1) 车1-7
 ------------------
 【下午】
-材料类(创新班)24(1) 车1-7
-环境科学25(1) 车5-7</t>
+材料类(创新班)24(1) 车1-7</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
@@ -7074,7 +7079,8 @@
           <t>【上午】
 环境工程25(1) 车1-4
 ------------------
-【下午】</t>
+【下午】
+应用化学24(4) 车5-7</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -7118,7 +7124,15 @@
 【下午】</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>【上午】
+应用化学24(2) 车1-4
+------------------
+【下午】
+应用化学24(3) 车5-7</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>【上午】
@@ -7163,7 +7177,7 @@
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>【上午】
-应用化学24(2) 车1-4
+环境工程25(2) 车1-4
 ------------------
 【下午】
 应用化学24(3) 车5-7</t>
@@ -7337,14 +7351,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>【上午】
-------------------
-【下午】
-应用化学24(4) 车5-7</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>【上午】
@@ -7472,14 +7479,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>【上午】
-------------------
-【下午】
-应用化学24(3) 车5-7</t>
-        </is>
-      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
 数字经济23(2) 钳1-4
 ------------------
 【下午】
-金融工程24(2) 钳5-7</t>
+金融工程24(2) 钳5-8</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
@@ -9258,7 +9258,7 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>【上午】
-应用化学24(1) 铸1-4（莫）
+应用化学24(1) 铸1-4
 ------------------
 【下午】</t>
         </is>
@@ -9294,7 +9294,7 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-交通运输25(1) 铸1-4（标）
+交通运输25(1) 铸1-4
 ------------------
 【下午】</t>
         </is>
@@ -9312,7 +9312,7 @@
           <t>【上午】
 ------------------
 【下午】
-环境生态工程(创新班)25(1) 铸5-7（标）</t>
+环境生态工程(创新班)25(1) 铸5-7</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -9349,19 +9349,11 @@
 【下午】</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>【上午】
-环境工程25(1) 铸1-4
-------------------
-【下午】
-应用化学24(3) 铸5-7（郭）</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-能源化学工程24(1) 铸1-4（莫）
+能源化学工程24(1) 铸1-4
 ------------------
 【下午】</t>
         </is>
@@ -9377,10 +9369,10 @@
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-电子科学与技术24(2) 铸1-4（标）
-------------------
-【下午】
-电子科学与技术24(4) 铸5-7（标、宋）</t>
+电子科学与技术24(2) 铸1-4
+------------------
+【下午】
+电子科学与技术24(4) 铸5-7</t>
         </is>
       </c>
     </row>
@@ -9394,6 +9386,7 @@
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>【上午】
+环境工程25(1) 铸1-4
 ------------------
 【下午】
 环境科学25(1) 铸5-7</t>
@@ -9402,10 +9395,10 @@
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>【上午】
-化学工程与工艺(创新班)24(1) 铸1-4（莫）
-------------------
-【下午】
-华师2 铸5-7（莫）</t>
+化学工程与工艺(创新班)24(1) 铸1-4
+------------------
+【下午】
+华师2 铸5-7</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9420,10 +9413,10 @@
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>【上午】
-华师3 铸1-4（钦）
-------------------
-【下午】
-电子科学与技术24(1) 铸5-7（钦）</t>
+华师3 铸1-4
+------------------
+【下午】
+电子科学与技术24(1) 铸5-7</t>
         </is>
       </c>
     </row>
@@ -9437,16 +9430,16 @@
       <c r="C9" s="3" t="inlineStr">
         <is>
           <t>【上午】
-应用化学24(2) 铸1-4（莫）
-------------------
-【下午】
-应用化学24(4) 铸5-7（莫）</t>
+应用化学24(2) 铸1-4
+------------------
+【下午】
+应用化学24(4) 铸5-7</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>【上午】
-能源化学工程24(2) 铸1-4（莫）
+能源化学工程24(2) 铸1-4
 ------------------
 【下午】</t>
         </is>
@@ -9454,10 +9447,10 @@
       <c r="E9" s="3" t="inlineStr">
         <is>
           <t>【上午】
-化学工程与工艺24(1) 铸1-4（标）
-------------------
-【下午】
-能源动力类25(1) 铸5-7（宋）</t>
+化学工程与工艺24(1) 铸1-4
+------------------
+【下午】
+能源动力类25(1) 铸5-7</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -9752,7 +9745,14 @@
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>【上午】
+------------------
+【下午】
+应用化学24(3) 铸5-7</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
@@ -9926,15 +9926,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>【上午】
-应用化学24(2) A齿1-2
-应用化学24(2) B齿3-4
-------------------
-【下午】</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -9946,7 +9938,15 @@
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>【上午】
+应用化学24(2) A齿1-2
+应用化学24(2) B齿3-4
+------------------
+【下午】</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
@@ -11120,7 +11120,7 @@
 数字媒体技术25(1)+(3)15人 先d1-4
 ------------------
 【下午】
-数字媒体技术25(1)+(3)15人 先d5-7（钦）</t>
+数字媒体技术25(1)+(3)15人 先d5-7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
           <t>【上午】
 ------------------
 【下午】
-电子科学与技术24(2) 先d5-7（钦）</t>
+电子科学与技术24(2) 先d5-7</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11231,7 @@
 化学工程与工艺(卓越工程师班)24(1) 先d1-4
 ------------------
 【下午】
-华师2 先d5-7（钦）</t>
+华师2 先d5-7</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -11282,7 +11282,7 @@
 工业工程24(1) 先d1-4
 ------------------
 【下午】
-计算机类25(1) 先d5-7（莲）</t>
+计算机类25(1) 先d5-7</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11778,10 +11778,10 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>【上午】
-计算机科学与技术(国际班)25(1)+中英班（6人） 先t4-7
-------------------
-【下午】
-计算机科学与技术(国际班)25(1)+中英班（6人） 先t4-7</t>
+计算机科学与技术(国际班)25(1)+中英班（6人） 先t4-8
+------------------
+【下午】
+计算机科学与技术(国际班)25(1)+中英班（6人） 先t4-8</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -11882,7 +11882,6 @@
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-环境工程25(1) 先t1-4
 ------------------
 【下午】
 环境生态工程(创新班)25(1) 先t5-7</t>
@@ -11945,6 +11944,7 @@
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>【上午】
+环境工程25(1) 先t1-4
 ------------------
 【下午】
 材料类(创新班)24(1) 先t5-7</t>
@@ -12514,8 +12514,7 @@
 应用化学24(2) A压1-2
 应用化学24(2) B压3-4
 ------------------
-【下午】
-环境科学25(1) 压5-7</t>
+【下午】</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
@@ -12527,7 +12526,7 @@
 ------------------
 【下午】
 金融工程24(1) A压5-6'
-金融工程24(1) B压6'-7</t>
+金融工程24(1) B压6'-8</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -12549,45 +12548,46 @@
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>【上午】
+数字经济23(2) A压1-2
+数字经济23(2) B压3-4
+------------------
+【下午】
+数字经济23(1) A压5-6'
+数字经济23(1) B压6'-7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>【上午】
+电子科学与技术(创新班)24(1) A压1-2
+电子科学与技术(创新班)24(1) B压3-4
+------------------
+【下午】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>第4周</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>【上午】
 环境工程25(1) A压1-2
 环境工程25(1) B压3-4
 ------------------
-【下午】</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>【上午】
-数字经济23(2) A压1-2
-数字经济23(2) B压3-4
-------------------
-【下午】
-数字经济23(1) A压5-6'
-数字经济23(1) B压6'-7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>【上午】
-电子科学与技术(创新班)24(1) A压1-2
-电子科学与技术(创新班)24(1) B压3-4
-------------------
-【下午】</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>第4周</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+【下午】
+环境科学25(1) 压5-7</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
@@ -13264,10 +13264,10 @@
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>【上午】
-制药工程24(2) 数c1-4(胡)
-------------------
-【下午】
-能源动力类25(3) 数c5-7(胡)</t>
+制药工程24(2) 数c1-4
+------------------
+【下午】
+能源动力类25(3) 数c5-7</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -13283,16 +13283,16 @@
           <t>【上午】
 ------------------
 【下午】
-数字媒体技术25(2)+(3)15人 数c5-7（胡）</t>
+数字媒体技术25(2)+(3)15人 数c5-7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>【上午】
-国际经济与贸易25(1) 数c1-4（胡）
-------------------
-【下午】
-国际经济与贸易25(2) 数c5-7（胡）</t>
+国际经济与贸易25(1) 数c1-4
+------------------
+【下午】
+国际经济与贸易25(2) 数c5-7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -13300,7 +13300,7 @@
           <t>【上午】
 ------------------
 【下午】
-能源动力类25(6) 数c5-7（胡）</t>
+能源动力类25(6) 数c5-7</t>
         </is>
       </c>
     </row>
@@ -13313,7 +13313,7 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-高分子材料与工程24(1) 数c1-4（柏）
+高分子材料与工程24(1) 数c1-4
 ------------------
 【下午】</t>
         </is>
@@ -13321,9 +13321,10 @@
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-应用化学24(1) 数c1-4（胡）
-------------------
-【下午】</t>
+应用化学24(1) 数c1-4
+------------------
+【下午】
+应用化学24(4) 数c5-7</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
@@ -13331,10 +13332,10 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-电子科学与技术24(3) 数c1-4（胡）
-------------------
-【下午】
-电子科学与技术24(1) 数c5-7（胡）</t>
+电子科学与技术24(3) 数c1-4
+------------------
+【下午】
+电子科学与技术24(1) 数c5-7</t>
         </is>
       </c>
     </row>
@@ -13345,14 +13346,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>【上午】
-------------------
-【下午】
-应用化学24(4) 数c5-7（胡）</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -13376,16 +13370,16 @@
 制药工程24(1) 数c1-4
 ------------------
 【下午】
-能源动力类25(5) 数c5-7（胡）</t>
+能源动力类25(5) 数c5-7</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-华师3 数c1-7（余）
-------------------
-【下午】
-华师3 数c1-7（余）</t>
+华师3 数c1-7
+------------------
+【下午】
+华师3 数c1-7</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -13393,7 +13387,7 @@
           <t>【上午】
 ------------------
 【下午】
-计算机类25(2) 数c5-7（胡）</t>
+计算机类25(2) 数c5-7</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -13401,16 +13395,16 @@
           <t>【上午】
 ------------------
 【下午】
-光电信息科学与工程24(1) 数c5-7（余）</t>
+光电信息科学与工程24(1) 数c5-7</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-华师2 数c1-7（余）
-------------------
-【下午】
-华师2 数c1-7（余）</t>
+华师2 数c1-7
+------------------
+【下午】
+华师2 数c1-7</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13419,7 @@
           <t>【上午】
 ------------------
 【下午】
-能源动力类25(2) 数c5-7（余）</t>
+能源动力类25(2) 数c5-7</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -13460,7 +13454,7 @@
       <c r="E9" s="3" t="inlineStr">
         <is>
           <t>【上午】
-化学工程与工艺24(2) 数c1-4（胡）
+化学工程与工艺24(2) 数c1-4
 ------------------
 【下午】
 计算机类25(16) 数c5-7</t>
@@ -13913,7 +13907,7 @@
           <t>【上午】
 ------------------
 【下午】
-金融工程24(1) 数x5-7</t>
+金融工程24(1) 数x5-8</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -13984,10 +13978,10 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>【上午】
-材料类(创新班)24(1) 数x1-4
-------------------
-【下午】
-材料类(创新班)24(1) 数x5-7</t>
+材料类(创新班)24(1) 数x1-7
+------------------
+【下午】
+材料类(创新班)24(1) 数x1-7</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -14104,7 +14098,7 @@
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>【上午】
-化学工程与工艺24(2) 数x1-4（杰）
+化学工程与工艺24(2) 数x1-4
 ------------------
 【下午】
 光电信息科学与工程24(3) 数x5-7</t>
@@ -14115,7 +14109,7 @@
           <t>【上午】
 ------------------
 【下午】
-电子科学与技术24(2) 数x5-7（柏）</t>
+电子科学与技术24(2) 数x5-7</t>
         </is>
       </c>
     </row>
@@ -14730,8 +14724,8 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-高分子材料与工程24(2) A智1-2（胡）
-高分子材料与工程24(2) B智3-4（胡）
+高分子材料与工程24(2) A智1-2
+高分子材料与工程24(2) B智3-4
 ------------------
 【下午】
 能源动力类25(3) A智5-7</t>
@@ -14759,10 +14753,10 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>【上午】
-电子科学与技术(创新班)24(1) A智1-7
-------------------
-【下午】
-电子科学与技术(创新班)24(1) A智1-7</t>
+电子科学与技术(创新班)24(1) A智1-4
+------------------
+【下午】
+电子科学与技术(创新班)24(1) B智5-7</t>
         </is>
       </c>
     </row>
@@ -14785,8 +14779,8 @@
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>【上午】
-能源化学工程24(1) A智1-2（胡）
-能源化学工程24(1) B智3-4（胡）
+能源化学工程24(1) A智1-2
+能源化学工程24(1) B智3-4
 ------------------
 【下午】
 计算机类25(1) A智5-7</t>
@@ -14805,10 +14799,10 @@
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>【上午】
-电子科学与技术(创新班)24(1) B智1-7
-------------------
-【下午】
-电子科学与技术(创新班)24(1) B智1-7</t>
+电子科学与技术(创新班)24(1) A智1-4
+------------------
+【下午】
+电子科学与技术(创新班)24(1) B智5-7</t>
         </is>
       </c>
     </row>
@@ -14945,8 +14939,8 @@
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>【上午】
-化学工程与工艺(卓越工程师班)24(1) A智1-2（胡）
-化学工程与工艺(卓越工程师班)24(1) B智3-4（胡）
+化学工程与工艺(卓越工程师班)24(1) A智1-2
+化学工程与工艺(卓越工程师班)24(1) B智3-4
 ------------------
 【下午】
 计算机类25(2) B智5-7</t>
